--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/KANSAS_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/KANSAS_2018.xlsx
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C159">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C252">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C588">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C792">
